--- a/Testkit_Q1_PRN222/Q12/TC6/Detail.xlsx
+++ b/Testkit_Q1_PRN222/Q12/TC6/Detail.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\PC\Documents\School\SEP490\networking\QuestionQ1_FA25\Testkit_Q1_PRN222\Q12\TC6\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\PC\Documents\School\NET\auto-grading\Testkit_Q1_PRN222\Q12\TC6\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0AA0EAB0-69C5-4ED6-B27A-A4E332045C41}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4E26B3C4-FBA5-4B6C-8D17-CDF9FE1C42CD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="User" sheetId="1" r:id="rId1"/>
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="205" uniqueCount="40">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="205" uniqueCount="38">
   <si>
     <t>Stage</t>
   </si>
@@ -44,13 +44,7 @@
     <t>StartServer</t>
   </si>
   <si>
-    <t xml:space="preserve"> Sabc</t>
-  </si>
-  <si>
     <t>CloseClient</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> S111</t>
   </si>
   <si>
     <t>Time</t>
@@ -570,7 +564,7 @@
         <v>3</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>6</v>
+        <v>30</v>
       </c>
       <c r="C4" s="3" t="s">
         <v>1</v>
@@ -584,7 +578,7 @@
         <v>3</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.3">
@@ -603,7 +597,7 @@
         <v>6</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>8</v>
+        <v>36</v>
       </c>
       <c r="C7" s="3" t="s">
         <v>1</v>
@@ -654,31 +648,31 @@
         <v>0</v>
       </c>
       <c r="B1" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D1" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="E1" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="F1" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="G1" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="F1" s="2" t="s">
+      <c r="H1" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="G1" s="2" t="s">
+      <c r="I1" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="H1" s="2" t="s">
+      <c r="J1" s="2" t="s">
         <v>15</v>
-      </c>
-      <c r="I1" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="J1" s="2" t="s">
-        <v>17</v>
       </c>
     </row>
     <row r="2" spans="1:10" ht="57.6" x14ac:dyDescent="0.3">
@@ -686,29 +680,29 @@
         <v>3</v>
       </c>
       <c r="B2" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="D2" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="C2" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="D2" s="3" t="s">
+      <c r="E2" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="F2" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="E2" s="3" t="s">
+      <c r="G2" s="3" t="s">
         <v>21</v>
-      </c>
-      <c r="F2" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="G2" s="3" t="s">
-        <v>23</v>
       </c>
       <c r="H2" s="3"/>
       <c r="I2" s="3" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="J2" s="3" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
     </row>
     <row r="3" spans="1:10" ht="43.2" x14ac:dyDescent="0.3">
@@ -716,29 +710,29 @@
         <v>3</v>
       </c>
       <c r="B3" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="D3" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="E3" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="C3" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="D3" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="E3" s="3" t="s">
-        <v>20</v>
-      </c>
       <c r="F3" s="3" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="H3" s="3"/>
       <c r="I3" s="3" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
     </row>
     <row r="4" spans="1:10" ht="57.6" x14ac:dyDescent="0.3">
@@ -746,29 +740,29 @@
         <v>3</v>
       </c>
       <c r="B4" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="D4" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="C4" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="D4" s="3" t="s">
-        <v>20</v>
-      </c>
       <c r="E4" s="3" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="H4" s="3"/>
       <c r="I4" s="3" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="J4" s="3" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
     </row>
     <row r="5" spans="1:10" ht="43.2" x14ac:dyDescent="0.3">
@@ -776,31 +770,31 @@
         <v>3</v>
       </c>
       <c r="B5" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="C5" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="D5" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="C5" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="D5" s="3" t="s">
-        <v>20</v>
-      </c>
       <c r="E5" s="3" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="F5" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="G5" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="H5" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="G5" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="H5" s="3" t="s">
-        <v>32</v>
-      </c>
       <c r="I5" s="3" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="J5" s="3" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
     </row>
     <row r="6" spans="1:10" ht="57.6" x14ac:dyDescent="0.3">
@@ -808,29 +802,29 @@
         <v>3</v>
       </c>
       <c r="B6" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="D6" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="E6" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="C6" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="D6" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="E6" s="3" t="s">
-        <v>20</v>
-      </c>
       <c r="F6" s="3" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="H6" s="3"/>
       <c r="I6" s="3" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="J6" s="3" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
     </row>
     <row r="7" spans="1:10" ht="230.4" x14ac:dyDescent="0.3">
@@ -838,31 +832,31 @@
         <v>3</v>
       </c>
       <c r="B7" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="D7" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="E7" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="C7" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="D7" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="E7" s="3" t="s">
-        <v>20</v>
-      </c>
       <c r="F7" s="3" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="G7" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="H7" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="H7" s="3" t="s">
-        <v>33</v>
-      </c>
       <c r="I7" s="3" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="J7" s="3" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
     </row>
     <row r="8" spans="1:10" ht="57.6" x14ac:dyDescent="0.3">
@@ -870,29 +864,29 @@
         <v>3</v>
       </c>
       <c r="B8" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="C8" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="D8" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="C8" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="D8" s="3" t="s">
-        <v>20</v>
-      </c>
       <c r="E8" s="3" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="H8" s="3"/>
       <c r="I8" s="3" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="J8" s="3" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
     </row>
     <row r="9" spans="1:10" ht="57.6" x14ac:dyDescent="0.3">
@@ -900,29 +894,29 @@
         <v>3</v>
       </c>
       <c r="B9" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="C9" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="D9" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="C9" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="D9" s="3" t="s">
-        <v>20</v>
-      </c>
       <c r="E9" s="3" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="F9" s="3" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="H9" s="3"/>
       <c r="I9" s="3" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="J9" s="3" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
     </row>
     <row r="10" spans="1:10" ht="57.6" x14ac:dyDescent="0.3">
@@ -930,29 +924,29 @@
         <v>3</v>
       </c>
       <c r="B10" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="C10" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="D10" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="E10" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="C10" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="D10" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="E10" s="3" t="s">
-        <v>20</v>
-      </c>
       <c r="F10" s="3" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="H10" s="3"/>
       <c r="I10" s="3" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="J10" s="3" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
     </row>
     <row r="11" spans="1:10" ht="57.6" x14ac:dyDescent="0.3">
@@ -960,29 +954,29 @@
         <v>3</v>
       </c>
       <c r="B11" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="C11" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="D11" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="E11" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="C11" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="D11" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="E11" s="3" t="s">
-        <v>20</v>
-      </c>
       <c r="F11" s="3" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="H11" s="3"/>
       <c r="I11" s="3" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="J11" s="3" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
     </row>
     <row r="12" spans="1:10" ht="57.6" x14ac:dyDescent="0.3">
@@ -990,29 +984,29 @@
         <v>3</v>
       </c>
       <c r="B12" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="C12" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="D12" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="C12" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="D12" s="3" t="s">
-        <v>20</v>
-      </c>
       <c r="E12" s="3" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="F12" s="3" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="G12" s="3" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="H12" s="3"/>
       <c r="I12" s="3" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="J12" s="3" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
     </row>
     <row r="13" spans="1:10" ht="57.6" x14ac:dyDescent="0.3">
@@ -1020,29 +1014,29 @@
         <v>6</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="E13" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="F13" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="G13" s="3" t="s">
         <v>21</v>
-      </c>
-      <c r="F13" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="G13" s="3" t="s">
-        <v>23</v>
       </c>
       <c r="H13" s="3"/>
       <c r="I13" s="3" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="J13" s="3" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
     </row>
     <row r="14" spans="1:10" ht="43.2" x14ac:dyDescent="0.3">
@@ -1050,29 +1044,29 @@
         <v>6</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="E14" s="3" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="F14" s="3" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="G14" s="3" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="H14" s="3"/>
       <c r="I14" s="3" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="J14" s="3" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
     </row>
     <row r="15" spans="1:10" ht="57.6" x14ac:dyDescent="0.3">
@@ -1080,29 +1074,29 @@
         <v>6</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="E15" s="3" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="F15" s="3" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="G15" s="3" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="H15" s="3"/>
       <c r="I15" s="3" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="J15" s="3" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
     </row>
     <row r="16" spans="1:10" ht="43.2" x14ac:dyDescent="0.3">
@@ -1110,31 +1104,31 @@
         <v>6</v>
       </c>
       <c r="B16" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="C16" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="D16" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="E16" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="F16" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="G16" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="H16" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="C16" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="D16" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="E16" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="F16" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="G16" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="H16" s="3" t="s">
-        <v>38</v>
-      </c>
       <c r="I16" s="3" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="J16" s="3" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
     </row>
     <row r="17" spans="1:10" ht="57.6" x14ac:dyDescent="0.3">
@@ -1142,29 +1136,29 @@
         <v>6</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="E17" s="3" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="F17" s="3" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="G17" s="3" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="H17" s="3"/>
       <c r="I17" s="3" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="J17" s="3" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
     </row>
     <row r="18" spans="1:10" ht="172.8" x14ac:dyDescent="0.3">
@@ -1172,31 +1166,31 @@
         <v>6</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="E18" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="F18" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="G18" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="H18" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="F18" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="G18" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="H18" s="3" t="s">
-        <v>39</v>
-      </c>
       <c r="I18" s="3" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="J18" s="3" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
     </row>
     <row r="19" spans="1:10" ht="57.6" x14ac:dyDescent="0.3">
@@ -1204,29 +1198,29 @@
         <v>6</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="E19" s="3" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="F19" s="3" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="G19" s="3" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="H19" s="3"/>
       <c r="I19" s="3" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="J19" s="3" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
     </row>
     <row r="20" spans="1:10" ht="57.6" x14ac:dyDescent="0.3">
@@ -1234,29 +1228,29 @@
         <v>6</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="E20" s="3" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="F20" s="3" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="G20" s="3" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="H20" s="3"/>
       <c r="I20" s="3" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="J20" s="3" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
     </row>
     <row r="21" spans="1:10" ht="57.6" x14ac:dyDescent="0.3">
@@ -1264,29 +1258,29 @@
         <v>6</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="E21" s="3" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="F21" s="3" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="G21" s="3" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="H21" s="3"/>
       <c r="I21" s="3" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="J21" s="3" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
     </row>
     <row r="22" spans="1:10" ht="57.6" x14ac:dyDescent="0.3">
@@ -1294,29 +1288,29 @@
         <v>6</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="D22" s="3" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="E22" s="3" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="F22" s="3" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="G22" s="3" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="H22" s="3"/>
       <c r="I22" s="3" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="J22" s="3" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
     </row>
     <row r="23" spans="1:10" ht="57.6" x14ac:dyDescent="0.3">
@@ -1324,29 +1318,29 @@
         <v>6</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="D23" s="3" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="E23" s="3" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="F23" s="3" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="G23" s="3" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="H23" s="3"/>
       <c r="I23" s="3" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="J23" s="3" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
     </row>
   </sheetData>
